--- a/data/satisfaction_detail/2026/1-6月/商务简餐.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/商务简餐.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>9.99</v>
@@ -514,7 +514,7 @@
         <v>9.93</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>9.960000000000001</v>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="14">
@@ -631,7 +631,7 @@
         <v>9.31</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="15">
